--- a/템플릿/행안부_30억미만_템플릿.xlsx
+++ b/템플릿/행안부_30억미만_템플릿.xlsx
@@ -1968,6 +1968,102 @@
     <xf numFmtId="41" fontId="8" fillId="6" borderId="12" xfId="56" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1991,102 +2087,6 @@
     </xf>
     <xf numFmtId="22" fontId="11" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="71">
@@ -2473,7 +2473,8 @@
     <col min="5" max="5" width="10.77734375" style="55" customWidth="1"/>
     <col min="6" max="7" width="9.21875" style="55" customWidth="1"/>
     <col min="8" max="8" width="6.6640625" style="55" customWidth="1"/>
-    <col min="9" max="10" width="7.33203125" style="55" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" style="55" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" style="55" customWidth="1"/>
     <col min="11" max="11" width="8.77734375" style="55" customWidth="1"/>
     <col min="12" max="13" width="6.77734375" style="55" customWidth="1"/>
     <col min="14" max="14" width="6.44140625" style="55" customWidth="1"/>
@@ -2502,74 +2503,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:46" ht="33.75" customHeight="1">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="148" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="135"/>
+      <c r="B1" s="149"/>
       <c r="C1" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="138"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="141"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="153"/>
+      <c r="F1" s="154"/>
+      <c r="G1" s="155"/>
       <c r="H1" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
+      <c r="I1" s="156"/>
+      <c r="J1" s="156"/>
       <c r="K1" s="92" t="e">
         <f>TRUNC(I1/F2,4)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="L1" s="68"/>
-      <c r="M1" s="143"/>
-      <c r="N1" s="143"/>
-      <c r="O1" s="143"/>
-      <c r="P1" s="143"/>
-      <c r="Q1" s="143"/>
-      <c r="R1" s="143"/>
-      <c r="S1" s="143"/>
-      <c r="T1" s="143"/>
-      <c r="U1" s="143"/>
-      <c r="V1" s="143"/>
-      <c r="W1" s="143"/>
-      <c r="X1" s="143"/>
-      <c r="Y1" s="143"/>
-      <c r="Z1" s="143"/>
-      <c r="AA1" s="143"/>
-      <c r="AB1" s="143"/>
-      <c r="AC1" s="143"/>
+      <c r="M1" s="157"/>
+      <c r="N1" s="157"/>
+      <c r="O1" s="157"/>
+      <c r="P1" s="157"/>
+      <c r="Q1" s="157"/>
+      <c r="R1" s="157"/>
+      <c r="S1" s="157"/>
+      <c r="T1" s="157"/>
+      <c r="U1" s="157"/>
+      <c r="V1" s="157"/>
+      <c r="W1" s="157"/>
+      <c r="X1" s="157"/>
+      <c r="Y1" s="157"/>
+      <c r="Z1" s="157"/>
+      <c r="AA1" s="157"/>
+      <c r="AB1" s="157"/>
+      <c r="AC1" s="157"/>
       <c r="AD1" s="106"/>
       <c r="AE1" s="106"/>
       <c r="AF1" s="106"/>
       <c r="AG1" s="106"/>
-      <c r="AH1" s="126"/>
-      <c r="AI1" s="126"/>
-      <c r="AJ1" s="126"/>
+      <c r="AH1" s="158"/>
+      <c r="AI1" s="158"/>
+      <c r="AJ1" s="158"/>
       <c r="AK1" s="107"/>
       <c r="AL1" s="107"/>
       <c r="AM1" s="107"/>
       <c r="AN1" s="107"/>
     </row>
     <row r="2" spans="1:46" s="58" customFormat="1" ht="30" customHeight="1" thickBot="1">
-      <c r="A2" s="136"/>
-      <c r="B2" s="137"/>
+      <c r="A2" s="150"/>
+      <c r="B2" s="151"/>
       <c r="C2" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="127"/>
-      <c r="E2" s="128"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="128"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="160"/>
       <c r="H2" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="130">
+      <c r="I2" s="162">
         <f>D2*0.8</f>
         <v>0</v>
       </c>
-      <c r="J2" s="131"/>
+      <c r="J2" s="163"/>
       <c r="K2" s="21" t="s">
         <v>27</v>
       </c>
@@ -2579,11 +2580,11 @@
       <c r="O2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="133"/>
-      <c r="R2" s="133"/>
-      <c r="S2" s="133"/>
-      <c r="T2" s="133"/>
+      <c r="P2" s="164"/>
+      <c r="Q2" s="165"/>
+      <c r="R2" s="165"/>
+      <c r="S2" s="165"/>
+      <c r="T2" s="165"/>
       <c r="U2" s="22"/>
       <c r="V2" s="22"/>
       <c r="W2" s="52"/>
@@ -2615,96 +2616,96 @@
       <c r="AT2" s="91"/>
     </row>
     <row r="3" spans="1:46" s="60" customFormat="1" ht="24.95" customHeight="1" thickBot="1">
-      <c r="A3" s="146" t="s">
+      <c r="A3" s="133" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="148" t="s">
+      <c r="B3" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="150" t="s">
+      <c r="C3" s="137" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="150"/>
-      <c r="E3" s="150"/>
-      <c r="F3" s="150"/>
-      <c r="G3" s="150"/>
-      <c r="H3" s="151"/>
-      <c r="I3" s="152" t="s">
+      <c r="D3" s="137"/>
+      <c r="E3" s="137"/>
+      <c r="F3" s="137"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="138"/>
+      <c r="I3" s="139" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="150"/>
-      <c r="K3" s="150"/>
-      <c r="L3" s="150"/>
-      <c r="M3" s="151"/>
-      <c r="N3" s="153" t="s">
+      <c r="J3" s="137"/>
+      <c r="K3" s="137"/>
+      <c r="L3" s="137"/>
+      <c r="M3" s="138"/>
+      <c r="N3" s="140" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="155" t="s">
+      <c r="O3" s="142" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="152" t="s">
+      <c r="P3" s="139" t="s">
         <v>6</v>
       </c>
-      <c r="Q3" s="150"/>
-      <c r="R3" s="150"/>
-      <c r="S3" s="150"/>
-      <c r="T3" s="150"/>
-      <c r="U3" s="151"/>
+      <c r="Q3" s="137"/>
+      <c r="R3" s="137"/>
+      <c r="S3" s="137"/>
+      <c r="T3" s="137"/>
+      <c r="U3" s="138"/>
       <c r="V3" s="59"/>
-      <c r="W3" s="152" t="s">
+      <c r="W3" s="139" t="s">
         <v>20</v>
       </c>
-      <c r="X3" s="150"/>
-      <c r="Y3" s="150"/>
-      <c r="Z3" s="150"/>
-      <c r="AA3" s="150"/>
-      <c r="AB3" s="150"/>
-      <c r="AC3" s="151"/>
+      <c r="X3" s="137"/>
+      <c r="Y3" s="137"/>
+      <c r="Z3" s="137"/>
+      <c r="AA3" s="137"/>
+      <c r="AB3" s="137"/>
+      <c r="AC3" s="138"/>
       <c r="AD3" s="59"/>
       <c r="AE3" s="59"/>
       <c r="AF3" s="59"/>
       <c r="AG3" s="59"/>
       <c r="AH3" s="71"/>
-      <c r="AI3" s="148" t="s">
+      <c r="AI3" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="AJ3" s="157" t="s">
+      <c r="AJ3" s="144" t="s">
         <v>8</v>
       </c>
-      <c r="AK3" s="159" t="s">
+      <c r="AK3" s="146" t="s">
         <v>9</v>
       </c>
-      <c r="AL3" s="144" t="s">
+      <c r="AL3" s="131" t="s">
         <v>10</v>
       </c>
-      <c r="AM3" s="162" t="s">
+      <c r="AM3" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="AN3" s="164" t="s">
+      <c r="AN3" s="129" t="s">
         <v>12</v>
       </c>
-      <c r="AO3" s="161" t="s">
+      <c r="AO3" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="AP3" s="161" t="s">
+      <c r="AP3" s="126" t="s">
         <v>32</v>
       </c>
-      <c r="AQ3" s="161" t="s">
+      <c r="AQ3" s="126" t="s">
         <v>33</v>
       </c>
-      <c r="AR3" s="161" t="s">
+      <c r="AR3" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="AS3" s="161" t="s">
+      <c r="AS3" s="126" t="s">
         <v>35</v>
       </c>
-      <c r="AT3" s="161" t="s">
+      <c r="AT3" s="126" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:46" s="60" customFormat="1" ht="39.75" customHeight="1" thickBot="1">
-      <c r="A4" s="147"/>
-      <c r="B4" s="149"/>
+      <c r="A4" s="134"/>
+      <c r="B4" s="136"/>
       <c r="C4" s="115" t="s">
         <v>13</v>
       </c>
@@ -2738,8 +2739,8 @@
       <c r="M4" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="154"/>
-      <c r="O4" s="156"/>
+      <c r="N4" s="141"/>
+      <c r="O4" s="143"/>
       <c r="P4" s="98" t="s">
         <v>13</v>
       </c>
@@ -2797,18 +2798,18 @@
       <c r="AH4" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="AI4" s="149"/>
-      <c r="AJ4" s="158"/>
-      <c r="AK4" s="160"/>
-      <c r="AL4" s="145"/>
-      <c r="AM4" s="163"/>
-      <c r="AN4" s="165"/>
-      <c r="AO4" s="161"/>
-      <c r="AP4" s="161"/>
-      <c r="AQ4" s="161"/>
-      <c r="AR4" s="161"/>
-      <c r="AS4" s="161"/>
-      <c r="AT4" s="161"/>
+      <c r="AI4" s="136"/>
+      <c r="AJ4" s="145"/>
+      <c r="AK4" s="147"/>
+      <c r="AL4" s="132"/>
+      <c r="AM4" s="128"/>
+      <c r="AN4" s="130"/>
+      <c r="AO4" s="126"/>
+      <c r="AP4" s="126"/>
+      <c r="AQ4" s="126"/>
+      <c r="AR4" s="126"/>
+      <c r="AS4" s="126"/>
+      <c r="AT4" s="126"/>
     </row>
     <row r="5" spans="1:46" s="85" customFormat="1" ht="50.25" customHeight="1" thickBot="1">
       <c r="A5" s="111"/>
@@ -14709,14 +14710,16 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="AS3:AS4"/>
-    <mergeCell ref="AT3:AT4"/>
-    <mergeCell ref="AM3:AM4"/>
-    <mergeCell ref="AN3:AN4"/>
-    <mergeCell ref="AO3:AO4"/>
-    <mergeCell ref="AP3:AP4"/>
-    <mergeCell ref="AQ3:AQ4"/>
-    <mergeCell ref="AR3:AR4"/>
+    <mergeCell ref="AH1:AJ1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="M1:AC1"/>
     <mergeCell ref="AL3:AL4"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
@@ -14729,16 +14732,14 @@
     <mergeCell ref="AI3:AI4"/>
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="M1:AC1"/>
-    <mergeCell ref="AH1:AJ1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="AS3:AS4"/>
+    <mergeCell ref="AT3:AT4"/>
+    <mergeCell ref="AM3:AM4"/>
+    <mergeCell ref="AN3:AN4"/>
+    <mergeCell ref="AO3:AO4"/>
+    <mergeCell ref="AP3:AP4"/>
+    <mergeCell ref="AQ3:AQ4"/>
+    <mergeCell ref="AR3:AR4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
